--- a/public/templates/ininjo/shiho_touki.xlsx
+++ b/public/templates/ininjo/shiho_touki.xlsx
@@ -752,7 +752,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="125">
+  <borders count="126">
     <border>
       <left/>
       <right/>
@@ -2202,11 +2202,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45"/>
   </cellStyleXfs>
-  <cellXfs count="634">
+  <cellXfs count="631">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -3612,25 +3613,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="58" fontId="12" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
@@ -3640,6 +3637,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -4695,60 +4693,60 @@
       <c r="W1" s="15" t="n"/>
       <c r="X1" s="15" t="n"/>
       <c r="Y1" s="15" t="n"/>
-      <c r="Z1" s="39" t="n"/>
-      <c r="AA1" s="39" t="n"/>
-      <c r="AB1" s="39" t="n"/>
-      <c r="AC1" s="39" t="n"/>
-      <c r="AD1" s="39" t="n"/>
-      <c r="AE1" s="39" t="n"/>
-      <c r="AF1" s="39" t="n"/>
-      <c r="AG1" s="39" t="n"/>
-      <c r="AH1" s="39" t="n"/>
-      <c r="AI1" s="39" t="n"/>
+      <c r="Z1" s="613" t="n"/>
+      <c r="AA1" s="613" t="n"/>
+      <c r="AB1" s="613" t="n"/>
+      <c r="AC1" s="613" t="n"/>
+      <c r="AD1" s="613" t="n"/>
+      <c r="AE1" s="613" t="n"/>
+      <c r="AF1" s="613" t="n"/>
+      <c r="AG1" s="613" t="n"/>
+      <c r="AH1" s="613" t="n"/>
+      <c r="AI1" s="613" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="359">
-      <c r="A2" s="613" t="inlineStr">
+      <c r="A2" s="614" t="inlineStr">
         <is>
           <t>委　任　状</t>
         </is>
       </c>
       <c r="Y2" s="15" t="n"/>
-      <c r="Z2" s="614" t="n"/>
-      <c r="AA2" s="615" t="n"/>
-      <c r="AB2" s="615" t="n"/>
+      <c r="Z2" s="615" t="n"/>
+      <c r="AA2" s="616" t="n"/>
+      <c r="AB2" s="616" t="n"/>
       <c r="AC2" s="616" t="n"/>
-      <c r="AD2" s="39" t="n"/>
-      <c r="AE2" s="39" t="n"/>
-      <c r="AF2" s="39" t="n"/>
-      <c r="AG2" s="39" t="n"/>
-      <c r="AH2" s="39" t="n"/>
-      <c r="AI2" s="39" t="n"/>
+      <c r="AD2" s="613" t="n"/>
+      <c r="AE2" s="613" t="n"/>
+      <c r="AF2" s="613" t="n"/>
+      <c r="AG2" s="613" t="n"/>
+      <c r="AH2" s="613" t="n"/>
+      <c r="AI2" s="613" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1" s="359">
       <c r="Y3" s="15" t="n"/>
       <c r="Z3" s="617" t="n"/>
-      <c r="AA3" s="618" t="n"/>
-      <c r="AB3" s="618" t="n"/>
-      <c r="AC3" s="619" t="n"/>
-      <c r="AD3" s="39" t="n"/>
-      <c r="AE3" s="39" t="n"/>
-      <c r="AF3" s="39" t="n"/>
-      <c r="AG3" s="39" t="n"/>
-      <c r="AH3" s="39" t="n"/>
-      <c r="AI3" s="39" t="n"/>
+      <c r="AA3" s="616" t="n"/>
+      <c r="AB3" s="616" t="n"/>
+      <c r="AC3" s="616" t="n"/>
+      <c r="AD3" s="613" t="n"/>
+      <c r="AE3" s="613" t="n"/>
+      <c r="AF3" s="613" t="n"/>
+      <c r="AG3" s="613" t="n"/>
+      <c r="AH3" s="613" t="n"/>
+      <c r="AI3" s="613" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1" s="359">
       <c r="Y4" s="15" t="n"/>
-      <c r="Z4" s="620" t="n"/>
-      <c r="AA4" s="621" t="n"/>
-      <c r="AB4" s="621" t="n"/>
-      <c r="AC4" s="622" t="n"/>
-      <c r="AD4" s="39" t="n"/>
-      <c r="AE4" s="39" t="n"/>
-      <c r="AF4" s="39" t="n"/>
-      <c r="AG4" s="39" t="n"/>
-      <c r="AH4" s="39" t="n"/>
-      <c r="AI4" s="39" t="n"/>
+      <c r="Z4" s="616" t="n"/>
+      <c r="AA4" s="616" t="n"/>
+      <c r="AB4" s="616" t="n"/>
+      <c r="AC4" s="616" t="n"/>
+      <c r="AD4" s="613" t="n"/>
+      <c r="AE4" s="613" t="n"/>
+      <c r="AF4" s="613" t="n"/>
+      <c r="AG4" s="613" t="n"/>
+      <c r="AH4" s="613" t="n"/>
+      <c r="AI4" s="613" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="359">
       <c r="A5" s="15" t="n"/>
@@ -4767,27 +4765,27 @@
       <c r="N5" s="15" t="n"/>
       <c r="O5" s="15" t="n"/>
       <c r="P5" s="15" t="n"/>
-      <c r="Q5" s="623" t="inlineStr">
+      <c r="Q5" s="618" t="inlineStr">
         <is>
           <t>令和</t>
         </is>
       </c>
-      <c r="S5" s="623" t="inlineStr">
+      <c r="S5" s="618" t="inlineStr">
         <is>
           <t xml:space="preserve">　　年　　　　月　　　　日</t>
         </is>
       </c>
       <c r="Y5" s="15" t="n"/>
-      <c r="Z5" s="39" t="n"/>
-      <c r="AA5" s="39" t="n"/>
-      <c r="AB5" s="39" t="n"/>
-      <c r="AC5" s="39" t="n"/>
-      <c r="AD5" s="39" t="n"/>
-      <c r="AE5" s="39" t="n"/>
-      <c r="AF5" s="39" t="n"/>
-      <c r="AG5" s="39" t="n"/>
-      <c r="AH5" s="39" t="n"/>
-      <c r="AI5" s="39" t="n"/>
+      <c r="Z5" s="613" t="n"/>
+      <c r="AA5" s="613" t="n"/>
+      <c r="AB5" s="613" t="n"/>
+      <c r="AC5" s="613" t="n"/>
+      <c r="AD5" s="613" t="n"/>
+      <c r="AE5" s="613" t="n"/>
+      <c r="AF5" s="613" t="n"/>
+      <c r="AG5" s="613" t="n"/>
+      <c r="AH5" s="613" t="n"/>
+      <c r="AI5" s="613" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="359">
       <c r="A6" s="15" t="n"/>
@@ -4815,16 +4813,16 @@
       <c r="W6" s="15" t="n"/>
       <c r="X6" s="15" t="n"/>
       <c r="Y6" s="15" t="n"/>
-      <c r="Z6" s="124" t="n"/>
-      <c r="AA6" s="127" t="n"/>
-      <c r="AB6" s="127" t="n"/>
-      <c r="AC6" s="127" t="n"/>
-      <c r="AD6" s="127" t="n"/>
-      <c r="AE6" s="127" t="n"/>
-      <c r="AF6" s="127" t="n"/>
-      <c r="AG6" s="127" t="n"/>
-      <c r="AH6" s="127" t="n"/>
-      <c r="AI6" s="128" t="n"/>
+      <c r="Z6" s="619" t="n"/>
+      <c r="AA6" s="613" t="n"/>
+      <c r="AB6" s="613" t="n"/>
+      <c r="AC6" s="613" t="n"/>
+      <c r="AD6" s="613" t="n"/>
+      <c r="AE6" s="613" t="n"/>
+      <c r="AF6" s="613" t="n"/>
+      <c r="AG6" s="613" t="n"/>
+      <c r="AH6" s="613" t="n"/>
+      <c r="AI6" s="613" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="359">
       <c r="A7" s="39" t="n"/>
@@ -4838,30 +4836,30 @@
       <c r="I7" s="39" t="n"/>
       <c r="J7" s="39" t="n"/>
       <c r="K7" s="39" t="n"/>
-      <c r="L7" s="624" t="inlineStr">
+      <c r="L7" s="620" t="inlineStr">
         <is>
           <t>委任者</t>
         </is>
       </c>
-      <c r="N7" s="625" t="inlineStr">
+      <c r="N7" s="621" t="inlineStr">
         <is>
           <t>（相続人）</t>
         </is>
       </c>
-      <c r="P7" s="625" t="n"/>
-      <c r="R7" s="624" t="n"/>
-      <c r="V7" s="625" t="n"/>
+      <c r="P7" s="621" t="n"/>
+      <c r="R7" s="620" t="n"/>
+      <c r="V7" s="621" t="n"/>
       <c r="Y7" s="15" t="n"/>
-      <c r="Z7" s="85" t="n"/>
-      <c r="AA7" s="39" t="n"/>
-      <c r="AB7" s="39" t="n"/>
-      <c r="AC7" s="39" t="n"/>
-      <c r="AD7" s="39" t="n"/>
-      <c r="AE7" s="39" t="n"/>
-      <c r="AF7" s="39" t="n"/>
-      <c r="AG7" s="39" t="n"/>
-      <c r="AH7" s="39" t="n"/>
-      <c r="AI7" s="86" t="n"/>
+      <c r="Z7" s="619" t="n"/>
+      <c r="AA7" s="613" t="n"/>
+      <c r="AB7" s="613" t="n"/>
+      <c r="AC7" s="613" t="n"/>
+      <c r="AD7" s="613" t="n"/>
+      <c r="AE7" s="613" t="n"/>
+      <c r="AF7" s="613" t="n"/>
+      <c r="AG7" s="613" t="n"/>
+      <c r="AH7" s="613" t="n"/>
+      <c r="AI7" s="613" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="359">
       <c r="A8" s="15" t="n"/>
@@ -4875,25 +4873,25 @@
       <c r="I8" s="39" t="n"/>
       <c r="J8" s="39" t="n"/>
       <c r="K8" s="39" t="n"/>
-      <c r="L8" s="624" t="inlineStr">
+      <c r="L8" s="620" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="N8" s="626" t="n"/>
+      <c r="N8" s="622" t="n"/>
       <c r="W8" s="139" t="n"/>
       <c r="X8" s="140" t="n"/>
       <c r="Y8" s="15" t="n"/>
-      <c r="Z8" s="129" t="n"/>
-      <c r="AA8" s="88" t="n"/>
-      <c r="AB8" s="88" t="n"/>
-      <c r="AC8" s="152" t="n"/>
-      <c r="AD8" s="152" t="n"/>
-      <c r="AE8" s="152" t="n"/>
-      <c r="AF8" s="152" t="n"/>
-      <c r="AG8" s="88" t="n"/>
-      <c r="AH8" s="88" t="n"/>
-      <c r="AI8" s="89" t="n"/>
+      <c r="Z8" s="623" t="n"/>
+      <c r="AA8" s="613" t="n"/>
+      <c r="AB8" s="613" t="n"/>
+      <c r="AC8" s="623" t="n"/>
+      <c r="AD8" s="623" t="n"/>
+      <c r="AE8" s="623" t="n"/>
+      <c r="AF8" s="623" t="n"/>
+      <c r="AG8" s="613" t="n"/>
+      <c r="AH8" s="613" t="n"/>
+      <c r="AI8" s="613" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="359">
       <c r="A9" s="15" t="n"/>
@@ -4910,27 +4908,27 @@
       <c r="L9" s="435" t="n"/>
       <c r="M9" s="435" t="n"/>
       <c r="N9" s="439" t="n"/>
-      <c r="O9" s="627" t="n"/>
-      <c r="P9" s="627" t="n"/>
-      <c r="Q9" s="627" t="n"/>
-      <c r="R9" s="627" t="n"/>
-      <c r="S9" s="627" t="n"/>
-      <c r="T9" s="627" t="n"/>
-      <c r="U9" s="627" t="n"/>
+      <c r="O9" s="624" t="n"/>
+      <c r="P9" s="624" t="n"/>
+      <c r="Q9" s="624" t="n"/>
+      <c r="R9" s="624" t="n"/>
+      <c r="S9" s="624" t="n"/>
+      <c r="T9" s="624" t="n"/>
+      <c r="U9" s="624" t="n"/>
       <c r="V9" s="141" t="n"/>
       <c r="W9" s="141" t="n"/>
       <c r="X9" s="141" t="n"/>
       <c r="Y9" s="15" t="n"/>
-      <c r="Z9" s="39" t="n"/>
-      <c r="AA9" s="39" t="n"/>
-      <c r="AB9" s="39" t="n"/>
-      <c r="AC9" s="39" t="n"/>
-      <c r="AD9" s="39" t="n"/>
-      <c r="AE9" s="39" t="n"/>
-      <c r="AF9" s="39" t="n"/>
-      <c r="AG9" s="39" t="n"/>
-      <c r="AH9" s="39" t="n"/>
-      <c r="AI9" s="39" t="n"/>
+      <c r="Z9" s="613" t="n"/>
+      <c r="AA9" s="613" t="n"/>
+      <c r="AB9" s="613" t="n"/>
+      <c r="AC9" s="613" t="n"/>
+      <c r="AD9" s="613" t="n"/>
+      <c r="AE9" s="613" t="n"/>
+      <c r="AF9" s="613" t="n"/>
+      <c r="AG9" s="613" t="n"/>
+      <c r="AH9" s="613" t="n"/>
+      <c r="AI9" s="613" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="359">
       <c r="A10" s="15" t="n"/>
@@ -4944,7 +4942,7 @@
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
-      <c r="L10" s="628" t="inlineStr">
+      <c r="L10" s="625" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
@@ -4961,16 +4959,16 @@
       <c r="W10" s="141" t="n"/>
       <c r="X10" s="141" t="n"/>
       <c r="Y10" s="15" t="n"/>
-      <c r="Z10" s="39" t="n"/>
-      <c r="AA10" s="39" t="n"/>
-      <c r="AB10" s="39" t="n"/>
-      <c r="AC10" s="39" t="n"/>
-      <c r="AD10" s="39" t="n"/>
-      <c r="AE10" s="39" t="n"/>
-      <c r="AF10" s="39" t="n"/>
-      <c r="AG10" s="39" t="n"/>
-      <c r="AH10" s="39" t="n"/>
-      <c r="AI10" s="39" t="n"/>
+      <c r="Z10" s="613" t="n"/>
+      <c r="AA10" s="613" t="n"/>
+      <c r="AB10" s="613" t="n"/>
+      <c r="AC10" s="613" t="n"/>
+      <c r="AD10" s="613" t="n"/>
+      <c r="AE10" s="613" t="n"/>
+      <c r="AF10" s="613" t="n"/>
+      <c r="AG10" s="613" t="n"/>
+      <c r="AH10" s="613" t="n"/>
+      <c r="AI10" s="613" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="359">
       <c r="A11" s="15" t="n"/>
@@ -5000,16 +4998,16 @@
         </is>
       </c>
       <c r="Y11" s="15" t="n"/>
-      <c r="Z11" s="39" t="n"/>
-      <c r="AA11" s="39" t="n"/>
-      <c r="AB11" s="39" t="n"/>
-      <c r="AC11" s="39" t="n"/>
-      <c r="AD11" s="39" t="n"/>
-      <c r="AE11" s="39" t="n"/>
-      <c r="AF11" s="39" t="n"/>
-      <c r="AG11" s="39" t="n"/>
-      <c r="AH11" s="39" t="n"/>
-      <c r="AI11" s="39" t="n"/>
+      <c r="Z11" s="613" t="n"/>
+      <c r="AA11" s="613" t="n"/>
+      <c r="AB11" s="613" t="n"/>
+      <c r="AC11" s="613" t="n"/>
+      <c r="AD11" s="613" t="n"/>
+      <c r="AE11" s="613" t="n"/>
+      <c r="AF11" s="613" t="n"/>
+      <c r="AG11" s="613" t="n"/>
+      <c r="AH11" s="613" t="n"/>
+      <c r="AI11" s="613" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="359">
       <c r="A12" s="15" t="n"/>
@@ -5030,7 +5028,7 @@
         </is>
       </c>
       <c r="N12" s="442" t="n"/>
-      <c r="O12" s="627" t="n"/>
+      <c r="O12" s="624" t="n"/>
       <c r="P12" s="148" t="n"/>
       <c r="Q12" s="148" t="inlineStr">
         <is>
@@ -5050,19 +5048,19 @@
         </is>
       </c>
       <c r="V12" s="15" t="n"/>
-      <c r="W12" s="629" t="n"/>
+      <c r="W12" s="626" t="n"/>
       <c r="X12" s="39" t="n"/>
       <c r="Y12" s="15" t="n"/>
-      <c r="Z12" s="39" t="n"/>
-      <c r="AA12" s="39" t="n"/>
-      <c r="AB12" s="39" t="n"/>
-      <c r="AC12" s="39" t="n"/>
-      <c r="AD12" s="39" t="n"/>
-      <c r="AE12" s="39" t="n"/>
-      <c r="AF12" s="39" t="n"/>
-      <c r="AG12" s="39" t="n"/>
-      <c r="AH12" s="39" t="n"/>
-      <c r="AI12" s="39" t="n"/>
+      <c r="Z12" s="613" t="n"/>
+      <c r="AA12" s="613" t="n"/>
+      <c r="AB12" s="613" t="n"/>
+      <c r="AC12" s="613" t="n"/>
+      <c r="AD12" s="613" t="n"/>
+      <c r="AE12" s="613" t="n"/>
+      <c r="AF12" s="613" t="n"/>
+      <c r="AG12" s="613" t="n"/>
+      <c r="AH12" s="613" t="n"/>
+      <c r="AI12" s="613" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="359">
       <c r="A13" s="15" t="n"/>
@@ -5090,25 +5088,25 @@
       <c r="W13" s="39" t="n"/>
       <c r="X13" s="15" t="n"/>
       <c r="Y13" s="15" t="n"/>
-      <c r="Z13" s="39" t="n"/>
-      <c r="AA13" s="39" t="n"/>
-      <c r="AB13" s="39" t="n"/>
-      <c r="AC13" s="39" t="n"/>
-      <c r="AD13" s="39" t="n"/>
-      <c r="AE13" s="39" t="n"/>
-      <c r="AF13" s="39" t="n"/>
-      <c r="AG13" s="39" t="n"/>
-      <c r="AH13" s="39" t="n"/>
-      <c r="AI13" s="39" t="n"/>
+      <c r="Z13" s="613" t="n"/>
+      <c r="AA13" s="613" t="n"/>
+      <c r="AB13" s="613" t="n"/>
+      <c r="AC13" s="613" t="n"/>
+      <c r="AD13" s="613" t="n"/>
+      <c r="AE13" s="613" t="n"/>
+      <c r="AF13" s="613" t="n"/>
+      <c r="AG13" s="613" t="n"/>
+      <c r="AH13" s="613" t="n"/>
+      <c r="AI13" s="613" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="359">
       <c r="A14" s="15" t="n"/>
-      <c r="B14" s="630" t="inlineStr">
+      <c r="B14" s="627" t="inlineStr">
         <is>
           <t>私は、被相続人</t>
         </is>
       </c>
-      <c r="F14" s="625" t="n"/>
+      <c r="F14" s="621" t="n"/>
       <c r="J14" s="80" t="inlineStr">
         <is>
           <t>（</t>
@@ -5141,16 +5139,16 @@
       <c r="W14" s="39" t="n"/>
       <c r="X14" s="15" t="n"/>
       <c r="Y14" s="15" t="n"/>
-      <c r="Z14" s="15" t="n"/>
-      <c r="AA14" s="15" t="n"/>
-      <c r="AB14" s="15" t="n"/>
-      <c r="AC14" s="15" t="n"/>
-      <c r="AD14" s="15" t="n"/>
-      <c r="AE14" s="15" t="n"/>
-      <c r="AF14" s="15" t="n"/>
-      <c r="AG14" s="15" t="n"/>
-      <c r="AH14" s="15" t="n"/>
-      <c r="AI14" s="15" t="n"/>
+      <c r="Z14" s="619" t="n"/>
+      <c r="AA14" s="619" t="n"/>
+      <c r="AB14" s="619" t="n"/>
+      <c r="AC14" s="619" t="n"/>
+      <c r="AD14" s="619" t="n"/>
+      <c r="AE14" s="619" t="n"/>
+      <c r="AF14" s="619" t="n"/>
+      <c r="AG14" s="619" t="n"/>
+      <c r="AH14" s="619" t="n"/>
+      <c r="AI14" s="619" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="359">
       <c r="A15" s="15" t="n"/>
@@ -5182,16 +5180,16 @@
       <c r="W15" s="15" t="n"/>
       <c r="X15" s="15" t="n"/>
       <c r="Y15" s="15" t="n"/>
-      <c r="Z15" s="15" t="n"/>
-      <c r="AA15" s="15" t="n"/>
-      <c r="AB15" s="15" t="n"/>
-      <c r="AC15" s="15" t="n"/>
-      <c r="AD15" s="15" t="n"/>
-      <c r="AE15" s="15" t="n"/>
-      <c r="AF15" s="15" t="n"/>
-      <c r="AG15" s="15" t="n"/>
-      <c r="AH15" s="15" t="n"/>
-      <c r="AI15" s="15" t="n"/>
+      <c r="Z15" s="619" t="n"/>
+      <c r="AA15" s="619" t="n"/>
+      <c r="AB15" s="619" t="n"/>
+      <c r="AC15" s="619" t="n"/>
+      <c r="AD15" s="619" t="n"/>
+      <c r="AE15" s="619" t="n"/>
+      <c r="AF15" s="619" t="n"/>
+      <c r="AG15" s="619" t="n"/>
+      <c r="AH15" s="619" t="n"/>
+      <c r="AI15" s="619" t="n"/>
     </row>
     <row r="16" ht="9.75" customHeight="1" s="359">
       <c r="A16" s="15" t="n"/>
@@ -5219,21 +5217,21 @@
       <c r="W16" s="39" t="n"/>
       <c r="X16" s="15" t="n"/>
       <c r="Y16" s="15" t="n"/>
-      <c r="Z16" s="39" t="n"/>
-      <c r="AA16" s="39" t="n"/>
-      <c r="AB16" s="39" t="n"/>
-      <c r="AC16" s="39" t="n"/>
-      <c r="AD16" s="39" t="n"/>
-      <c r="AE16" s="39" t="n"/>
-      <c r="AF16" s="39" t="n"/>
-      <c r="AG16" s="39" t="n"/>
-      <c r="AH16" s="39" t="n"/>
-      <c r="AI16" s="39" t="n"/>
+      <c r="Z16" s="613" t="n"/>
+      <c r="AA16" s="613" t="n"/>
+      <c r="AB16" s="613" t="n"/>
+      <c r="AC16" s="613" t="n"/>
+      <c r="AD16" s="613" t="n"/>
+      <c r="AE16" s="613" t="n"/>
+      <c r="AF16" s="613" t="n"/>
+      <c r="AG16" s="613" t="n"/>
+      <c r="AH16" s="613" t="n"/>
+      <c r="AI16" s="613" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="359">
       <c r="A17" s="15" t="n"/>
       <c r="B17" s="15" t="n"/>
-      <c r="C17" s="625" t="inlineStr">
+      <c r="C17" s="621" t="inlineStr">
         <is>
           <t>代　理　人</t>
         </is>
@@ -5258,26 +5256,26 @@
       <c r="W17" s="39" t="n"/>
       <c r="X17" s="15" t="n"/>
       <c r="Y17" s="15" t="n"/>
-      <c r="Z17" s="39" t="n"/>
-      <c r="AA17" s="39" t="n"/>
-      <c r="AB17" s="39" t="n"/>
-      <c r="AC17" s="39" t="n"/>
-      <c r="AD17" s="39" t="n"/>
-      <c r="AE17" s="39" t="n"/>
-      <c r="AF17" s="39" t="n"/>
-      <c r="AG17" s="39" t="n"/>
-      <c r="AH17" s="39" t="n"/>
-      <c r="AI17" s="39" t="n"/>
+      <c r="Z17" s="613" t="n"/>
+      <c r="AA17" s="613" t="n"/>
+      <c r="AB17" s="613" t="n"/>
+      <c r="AC17" s="613" t="n"/>
+      <c r="AD17" s="613" t="n"/>
+      <c r="AE17" s="613" t="n"/>
+      <c r="AF17" s="613" t="n"/>
+      <c r="AG17" s="613" t="n"/>
+      <c r="AH17" s="613" t="n"/>
+      <c r="AI17" s="613" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="359">
       <c r="A18" s="15" t="n"/>
       <c r="B18" s="15" t="n"/>
-      <c r="C18" s="624" t="inlineStr">
+      <c r="C18" s="620" t="inlineStr">
         <is>
           <t>本店住所</t>
         </is>
       </c>
-      <c r="G18" s="631" t="inlineStr">
+      <c r="G18" s="628" t="inlineStr">
         <is>
           <t>横浜市西区高島２丁目１３－２ 横浜駅前共同ビル</t>
         </is>
@@ -5285,26 +5283,26 @@
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="15" t="n"/>
       <c r="Y18" s="15" t="n"/>
-      <c r="Z18" s="15" t="n"/>
-      <c r="AA18" s="15" t="n"/>
-      <c r="AB18" s="15" t="n"/>
-      <c r="AC18" s="15" t="n"/>
-      <c r="AD18" s="15" t="n"/>
-      <c r="AE18" s="15" t="n"/>
-      <c r="AF18" s="15" t="n"/>
-      <c r="AG18" s="15" t="n"/>
-      <c r="AH18" s="15" t="n"/>
-      <c r="AI18" s="15" t="n"/>
+      <c r="Z18" s="619" t="n"/>
+      <c r="AA18" s="619" t="n"/>
+      <c r="AB18" s="619" t="n"/>
+      <c r="AC18" s="619" t="n"/>
+      <c r="AD18" s="619" t="n"/>
+      <c r="AE18" s="619" t="n"/>
+      <c r="AF18" s="619" t="n"/>
+      <c r="AG18" s="619" t="n"/>
+      <c r="AH18" s="619" t="n"/>
+      <c r="AI18" s="619" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="359">
       <c r="A19" s="15" t="n"/>
       <c r="B19" s="15" t="n"/>
-      <c r="C19" s="625" t="inlineStr">
+      <c r="C19" s="621" t="inlineStr">
         <is>
           <t>従たる事務所</t>
         </is>
       </c>
-      <c r="G19" s="631" t="inlineStr">
+      <c r="G19" s="628" t="inlineStr">
         <is>
           <t>横浜市西区高島二丁目１４番１７号　クレアトール横浜ビル５階</t>
         </is>
@@ -5312,16 +5310,16 @@
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="15" t="n"/>
       <c r="Y19" s="15" t="n"/>
-      <c r="Z19" s="15" t="n"/>
-      <c r="AA19" s="15" t="n"/>
-      <c r="AB19" s="15" t="n"/>
-      <c r="AC19" s="15" t="n"/>
-      <c r="AD19" s="15" t="n"/>
-      <c r="AE19" s="15" t="n"/>
-      <c r="AF19" s="15" t="n"/>
-      <c r="AG19" s="15" t="n"/>
-      <c r="AH19" s="15" t="n"/>
-      <c r="AI19" s="15" t="n"/>
+      <c r="Z19" s="619" t="n"/>
+      <c r="AA19" s="619" t="n"/>
+      <c r="AB19" s="619" t="n"/>
+      <c r="AC19" s="619" t="n"/>
+      <c r="AD19" s="619" t="n"/>
+      <c r="AE19" s="619" t="n"/>
+      <c r="AF19" s="619" t="n"/>
+      <c r="AG19" s="619" t="n"/>
+      <c r="AH19" s="619" t="n"/>
+      <c r="AI19" s="619" t="n"/>
     </row>
     <row r="20" ht="9.75" customHeight="1" s="359">
       <c r="A20" s="15" t="n"/>
@@ -5349,28 +5347,28 @@
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="n"/>
-      <c r="Z20" s="15" t="n"/>
-      <c r="AA20" s="15" t="n"/>
-      <c r="AB20" s="15" t="n"/>
-      <c r="AC20" s="15" t="n"/>
-      <c r="AD20" s="15" t="n"/>
-      <c r="AE20" s="15" t="n"/>
-      <c r="AF20" s="15" t="n"/>
-      <c r="AG20" s="15" t="n"/>
-      <c r="AH20" s="15" t="n"/>
-      <c r="AI20" s="15" t="n"/>
+      <c r="Z20" s="619" t="n"/>
+      <c r="AA20" s="619" t="n"/>
+      <c r="AB20" s="619" t="n"/>
+      <c r="AC20" s="619" t="n"/>
+      <c r="AD20" s="619" t="n"/>
+      <c r="AE20" s="619" t="n"/>
+      <c r="AF20" s="619" t="n"/>
+      <c r="AG20" s="619" t="n"/>
+      <c r="AH20" s="619" t="n"/>
+      <c r="AI20" s="619" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="359">
       <c r="A21" s="15" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="15" t="n"/>
       <c r="D21" s="15" t="n"/>
-      <c r="E21" s="628" t="inlineStr">
+      <c r="E21" s="625" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="G21" s="632" t="inlineStr">
+      <c r="G21" s="629" t="inlineStr">
         <is>
           <t>司法書士法人オーシャン　　 　代表社員　　山田　哲</t>
         </is>
@@ -5380,16 +5378,16 @@
       <c r="W21" s="15" t="n"/>
       <c r="X21" s="15" t="n"/>
       <c r="Y21" s="15" t="n"/>
-      <c r="Z21" s="15" t="n"/>
-      <c r="AA21" s="15" t="n"/>
-      <c r="AB21" s="15" t="n"/>
-      <c r="AC21" s="15" t="n"/>
-      <c r="AD21" s="15" t="n"/>
-      <c r="AE21" s="15" t="n"/>
-      <c r="AF21" s="15" t="n"/>
-      <c r="AG21" s="15" t="n"/>
-      <c r="AH21" s="15" t="n"/>
-      <c r="AI21" s="15" t="n"/>
+      <c r="Z21" s="619" t="n"/>
+      <c r="AA21" s="619" t="n"/>
+      <c r="AB21" s="619" t="n"/>
+      <c r="AC21" s="619" t="n"/>
+      <c r="AD21" s="619" t="n"/>
+      <c r="AE21" s="619" t="n"/>
+      <c r="AF21" s="619" t="n"/>
+      <c r="AG21" s="619" t="n"/>
+      <c r="AH21" s="619" t="n"/>
+      <c r="AI21" s="619" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="359">
       <c r="A22" s="15" t="n"/>
@@ -5401,16 +5399,16 @@
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="15" t="n"/>
       <c r="Y22" s="15" t="n"/>
-      <c r="Z22" s="15" t="n"/>
-      <c r="AA22" s="15" t="n"/>
-      <c r="AB22" s="15" t="n"/>
-      <c r="AC22" s="15" t="n"/>
-      <c r="AD22" s="15" t="n"/>
-      <c r="AE22" s="15" t="n"/>
-      <c r="AF22" s="15" t="n"/>
-      <c r="AG22" s="15" t="n"/>
-      <c r="AH22" s="15" t="n"/>
-      <c r="AI22" s="15" t="n"/>
+      <c r="Z22" s="619" t="n"/>
+      <c r="AA22" s="619" t="n"/>
+      <c r="AB22" s="619" t="n"/>
+      <c r="AC22" s="619" t="n"/>
+      <c r="AD22" s="619" t="n"/>
+      <c r="AE22" s="619" t="n"/>
+      <c r="AF22" s="619" t="n"/>
+      <c r="AG22" s="619" t="n"/>
+      <c r="AH22" s="619" t="n"/>
+      <c r="AI22" s="619" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="359">
       <c r="A23" s="15" t="n"/>
@@ -5438,24 +5436,34 @@
       <c r="W23" s="39" t="n"/>
       <c r="X23" s="15" t="n"/>
       <c r="Y23" s="15" t="n"/>
-      <c r="Z23" s="39" t="n"/>
-      <c r="AA23" s="39" t="n"/>
-      <c r="AB23" s="39" t="n"/>
-      <c r="AC23" s="39" t="n"/>
-      <c r="AD23" s="39" t="n"/>
-      <c r="AE23" s="39" t="n"/>
-      <c r="AF23" s="39" t="n"/>
-      <c r="AG23" s="39" t="n"/>
-      <c r="AH23" s="39" t="n"/>
-      <c r="AI23" s="39" t="n"/>
+      <c r="Z23" s="613" t="n"/>
+      <c r="AA23" s="613" t="n"/>
+      <c r="AB23" s="613" t="n"/>
+      <c r="AC23" s="613" t="n"/>
+      <c r="AD23" s="613" t="n"/>
+      <c r="AE23" s="613" t="n"/>
+      <c r="AF23" s="613" t="n"/>
+      <c r="AG23" s="613" t="n"/>
+      <c r="AH23" s="613" t="n"/>
+      <c r="AI23" s="613" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="359">
-      <c r="A24" s="633" t="inlineStr">
+      <c r="A24" s="630" t="inlineStr">
         <is>
           <t>記</t>
         </is>
       </c>
       <c r="Y24" s="15" t="n"/>
+      <c r="Z24" s="616" t="n"/>
+      <c r="AA24" s="616" t="n"/>
+      <c r="AB24" s="616" t="n"/>
+      <c r="AC24" s="616" t="n"/>
+      <c r="AD24" s="616" t="n"/>
+      <c r="AE24" s="616" t="n"/>
+      <c r="AF24" s="616" t="n"/>
+      <c r="AG24" s="616" t="n"/>
+      <c r="AH24" s="616" t="n"/>
+      <c r="AI24" s="616" t="n"/>
     </row>
     <row r="25" ht="9.75" customHeight="1" s="359">
       <c r="A25" s="15" t="n"/>
@@ -5483,16 +5491,16 @@
       <c r="W25" s="39" t="n"/>
       <c r="X25" s="15" t="n"/>
       <c r="Y25" s="15" t="n"/>
-      <c r="Z25" s="39" t="n"/>
-      <c r="AA25" s="39" t="n"/>
-      <c r="AB25" s="39" t="n"/>
-      <c r="AC25" s="39" t="n"/>
-      <c r="AD25" s="39" t="n"/>
-      <c r="AE25" s="39" t="n"/>
-      <c r="AF25" s="39" t="n"/>
-      <c r="AG25" s="39" t="n"/>
-      <c r="AH25" s="39" t="n"/>
-      <c r="AI25" s="39" t="n"/>
+      <c r="Z25" s="613" t="n"/>
+      <c r="AA25" s="613" t="n"/>
+      <c r="AB25" s="613" t="n"/>
+      <c r="AC25" s="613" t="n"/>
+      <c r="AD25" s="613" t="n"/>
+      <c r="AE25" s="613" t="n"/>
+      <c r="AF25" s="613" t="n"/>
+      <c r="AG25" s="613" t="n"/>
+      <c r="AH25" s="613" t="n"/>
+      <c r="AI25" s="613" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="359">
       <c r="A26" s="15" t="n"/>
@@ -5526,6 +5534,16 @@
       <c r="W26" s="15" t="n"/>
       <c r="X26" s="15" t="n"/>
       <c r="Y26" s="15" t="n"/>
+      <c r="Z26" s="616" t="n"/>
+      <c r="AA26" s="616" t="n"/>
+      <c r="AB26" s="616" t="n"/>
+      <c r="AC26" s="616" t="n"/>
+      <c r="AD26" s="616" t="n"/>
+      <c r="AE26" s="616" t="n"/>
+      <c r="AF26" s="616" t="n"/>
+      <c r="AG26" s="616" t="n"/>
+      <c r="AH26" s="616" t="n"/>
+      <c r="AI26" s="616" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="359">
       <c r="A27" s="15" t="n"/>
@@ -5560,6 +5578,16 @@
       <c r="W27" s="15" t="n"/>
       <c r="X27" s="15" t="n"/>
       <c r="Y27" s="15" t="n"/>
+      <c r="Z27" s="616" t="n"/>
+      <c r="AA27" s="616" t="n"/>
+      <c r="AB27" s="616" t="n"/>
+      <c r="AC27" s="616" t="n"/>
+      <c r="AD27" s="616" t="n"/>
+      <c r="AE27" s="616" t="n"/>
+      <c r="AF27" s="616" t="n"/>
+      <c r="AG27" s="616" t="n"/>
+      <c r="AH27" s="616" t="n"/>
+      <c r="AI27" s="616" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="359">
       <c r="A28" s="15" t="n"/>
@@ -5590,6 +5618,16 @@
       <c r="W28" s="15" t="n"/>
       <c r="X28" s="15" t="n"/>
       <c r="Y28" s="15" t="n"/>
+      <c r="Z28" s="616" t="n"/>
+      <c r="AA28" s="616" t="n"/>
+      <c r="AB28" s="616" t="n"/>
+      <c r="AC28" s="616" t="n"/>
+      <c r="AD28" s="616" t="n"/>
+      <c r="AE28" s="616" t="n"/>
+      <c r="AF28" s="616" t="n"/>
+      <c r="AG28" s="616" t="n"/>
+      <c r="AH28" s="616" t="n"/>
+      <c r="AI28" s="616" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="359">
       <c r="A29" s="15" t="n"/>
@@ -5624,6 +5662,16 @@
       <c r="W29" s="15" t="n"/>
       <c r="X29" s="15" t="n"/>
       <c r="Y29" s="15" t="n"/>
+      <c r="Z29" s="616" t="n"/>
+      <c r="AA29" s="616" t="n"/>
+      <c r="AB29" s="616" t="n"/>
+      <c r="AC29" s="616" t="n"/>
+      <c r="AD29" s="616" t="n"/>
+      <c r="AE29" s="616" t="n"/>
+      <c r="AF29" s="616" t="n"/>
+      <c r="AG29" s="616" t="n"/>
+      <c r="AH29" s="616" t="n"/>
+      <c r="AI29" s="616" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="359">
       <c r="A30" s="15" t="n"/>
@@ -5658,6 +5706,16 @@
       <c r="W30" s="15" t="n"/>
       <c r="X30" s="15" t="n"/>
       <c r="Y30" s="15" t="n"/>
+      <c r="Z30" s="616" t="n"/>
+      <c r="AA30" s="616" t="n"/>
+      <c r="AB30" s="616" t="n"/>
+      <c r="AC30" s="616" t="n"/>
+      <c r="AD30" s="616" t="n"/>
+      <c r="AE30" s="616" t="n"/>
+      <c r="AF30" s="616" t="n"/>
+      <c r="AG30" s="616" t="n"/>
+      <c r="AH30" s="616" t="n"/>
+      <c r="AI30" s="616" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="359">
       <c r="A31" s="15" t="n"/>
@@ -5692,6 +5750,16 @@
       <c r="W31" s="15" t="n"/>
       <c r="X31" s="15" t="n"/>
       <c r="Y31" s="15" t="n"/>
+      <c r="Z31" s="616" t="n"/>
+      <c r="AA31" s="616" t="n"/>
+      <c r="AB31" s="616" t="n"/>
+      <c r="AC31" s="616" t="n"/>
+      <c r="AD31" s="616" t="n"/>
+      <c r="AE31" s="616" t="n"/>
+      <c r="AF31" s="616" t="n"/>
+      <c r="AG31" s="616" t="n"/>
+      <c r="AH31" s="616" t="n"/>
+      <c r="AI31" s="616" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="359">
       <c r="A32" s="15" t="n"/>
@@ -5719,6 +5787,16 @@
       <c r="W32" s="15" t="n"/>
       <c r="X32" s="15" t="n"/>
       <c r="Y32" s="15" t="n"/>
+      <c r="Z32" s="616" t="n"/>
+      <c r="AA32" s="616" t="n"/>
+      <c r="AB32" s="616" t="n"/>
+      <c r="AC32" s="616" t="n"/>
+      <c r="AD32" s="616" t="n"/>
+      <c r="AE32" s="616" t="n"/>
+      <c r="AF32" s="616" t="n"/>
+      <c r="AG32" s="616" t="n"/>
+      <c r="AH32" s="616" t="n"/>
+      <c r="AI32" s="616" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="359">
       <c r="A33" s="15" t="n"/>
@@ -5744,6 +5822,16 @@
       <c r="W33" s="15" t="n"/>
       <c r="X33" s="15" t="n"/>
       <c r="Y33" s="15" t="n"/>
+      <c r="Z33" s="616" t="n"/>
+      <c r="AA33" s="616" t="n"/>
+      <c r="AB33" s="616" t="n"/>
+      <c r="AC33" s="616" t="n"/>
+      <c r="AD33" s="616" t="n"/>
+      <c r="AE33" s="616" t="n"/>
+      <c r="AF33" s="616" t="n"/>
+      <c r="AG33" s="616" t="n"/>
+      <c r="AH33" s="616" t="n"/>
+      <c r="AI33" s="616" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="359">
       <c r="A34" s="15" t="n"/>
@@ -5779,6 +5867,16 @@
       <c r="W34" s="15" t="n"/>
       <c r="X34" s="15" t="n"/>
       <c r="Y34" s="15" t="n"/>
+      <c r="Z34" s="616" t="n"/>
+      <c r="AA34" s="616" t="n"/>
+      <c r="AB34" s="616" t="n"/>
+      <c r="AC34" s="616" t="n"/>
+      <c r="AD34" s="616" t="n"/>
+      <c r="AE34" s="616" t="n"/>
+      <c r="AF34" s="616" t="n"/>
+      <c r="AG34" s="616" t="n"/>
+      <c r="AH34" s="616" t="n"/>
+      <c r="AI34" s="616" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1" s="359">
       <c r="A35" s="15" t="n"/>
@@ -5803,6 +5901,16 @@
       <c r="W35" s="15" t="n"/>
       <c r="X35" s="15" t="n"/>
       <c r="Y35" s="15" t="n"/>
+      <c r="Z35" s="616" t="n"/>
+      <c r="AA35" s="616" t="n"/>
+      <c r="AB35" s="616" t="n"/>
+      <c r="AC35" s="616" t="n"/>
+      <c r="AD35" s="616" t="n"/>
+      <c r="AE35" s="616" t="n"/>
+      <c r="AF35" s="616" t="n"/>
+      <c r="AG35" s="616" t="n"/>
+      <c r="AH35" s="616" t="n"/>
+      <c r="AI35" s="616" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1" s="359">
       <c r="A36" s="15" t="n"/>
@@ -5827,6 +5935,16 @@
       <c r="W36" s="15" t="n"/>
       <c r="X36" s="15" t="n"/>
       <c r="Y36" s="15" t="n"/>
+      <c r="Z36" s="616" t="n"/>
+      <c r="AA36" s="616" t="n"/>
+      <c r="AB36" s="616" t="n"/>
+      <c r="AC36" s="616" t="n"/>
+      <c r="AD36" s="616" t="n"/>
+      <c r="AE36" s="616" t="n"/>
+      <c r="AF36" s="616" t="n"/>
+      <c r="AG36" s="616" t="n"/>
+      <c r="AH36" s="616" t="n"/>
+      <c r="AI36" s="616" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="359">
       <c r="A37" s="15" t="n"/>
@@ -5862,6 +5980,16 @@
       <c r="W37" s="15" t="n"/>
       <c r="X37" s="15" t="n"/>
       <c r="Y37" s="15" t="n"/>
+      <c r="Z37" s="616" t="n"/>
+      <c r="AA37" s="616" t="n"/>
+      <c r="AB37" s="616" t="n"/>
+      <c r="AC37" s="616" t="n"/>
+      <c r="AD37" s="616" t="n"/>
+      <c r="AE37" s="616" t="n"/>
+      <c r="AF37" s="616" t="n"/>
+      <c r="AG37" s="616" t="n"/>
+      <c r="AH37" s="616" t="n"/>
+      <c r="AI37" s="616" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="359">
       <c r="A38" s="15" t="n"/>
@@ -5888,6 +6016,16 @@
       <c r="W38" s="15" t="n"/>
       <c r="X38" s="15" t="n"/>
       <c r="Y38" s="15" t="n"/>
+      <c r="Z38" s="616" t="n"/>
+      <c r="AA38" s="616" t="n"/>
+      <c r="AB38" s="616" t="n"/>
+      <c r="AC38" s="616" t="n"/>
+      <c r="AD38" s="616" t="n"/>
+      <c r="AE38" s="616" t="n"/>
+      <c r="AF38" s="616" t="n"/>
+      <c r="AG38" s="616" t="n"/>
+      <c r="AH38" s="616" t="n"/>
+      <c r="AI38" s="616" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="359">
       <c r="A39" s="15" t="n"/>
@@ -5913,6 +6051,16 @@
       <c r="W39" s="15" t="n"/>
       <c r="X39" s="15" t="n"/>
       <c r="Y39" s="15" t="n"/>
+      <c r="Z39" s="616" t="n"/>
+      <c r="AA39" s="616" t="n"/>
+      <c r="AB39" s="616" t="n"/>
+      <c r="AC39" s="616" t="n"/>
+      <c r="AD39" s="616" t="n"/>
+      <c r="AE39" s="616" t="n"/>
+      <c r="AF39" s="616" t="n"/>
+      <c r="AG39" s="616" t="n"/>
+      <c r="AH39" s="616" t="n"/>
+      <c r="AI39" s="616" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="359">
       <c r="A40" s="15" t="n"/>
@@ -5946,6 +6094,16 @@
       <c r="W40" s="15" t="n"/>
       <c r="X40" s="15" t="n"/>
       <c r="Y40" s="15" t="n"/>
+      <c r="Z40" s="616" t="n"/>
+      <c r="AA40" s="616" t="n"/>
+      <c r="AB40" s="616" t="n"/>
+      <c r="AC40" s="616" t="n"/>
+      <c r="AD40" s="616" t="n"/>
+      <c r="AE40" s="616" t="n"/>
+      <c r="AF40" s="616" t="n"/>
+      <c r="AG40" s="616" t="n"/>
+      <c r="AH40" s="616" t="n"/>
+      <c r="AI40" s="616" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="359">
       <c r="A41" s="15" t="n"/>
@@ -5973,6 +6131,16 @@
       <c r="W41" s="15" t="n"/>
       <c r="X41" s="15" t="n"/>
       <c r="Y41" s="15" t="n"/>
+      <c r="Z41" s="616" t="n"/>
+      <c r="AA41" s="616" t="n"/>
+      <c r="AB41" s="616" t="n"/>
+      <c r="AC41" s="616" t="n"/>
+      <c r="AD41" s="616" t="n"/>
+      <c r="AE41" s="616" t="n"/>
+      <c r="AF41" s="616" t="n"/>
+      <c r="AG41" s="616" t="n"/>
+      <c r="AH41" s="616" t="n"/>
+      <c r="AI41" s="616" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="359">
       <c r="A42" s="15" t="n"/>
@@ -6000,6 +6168,16 @@
       <c r="W42" s="15" t="n"/>
       <c r="X42" s="15" t="n"/>
       <c r="Y42" s="15" t="n"/>
+      <c r="Z42" s="616" t="n"/>
+      <c r="AA42" s="616" t="n"/>
+      <c r="AB42" s="616" t="n"/>
+      <c r="AC42" s="616" t="n"/>
+      <c r="AD42" s="616" t="n"/>
+      <c r="AE42" s="616" t="n"/>
+      <c r="AF42" s="616" t="n"/>
+      <c r="AG42" s="616" t="n"/>
+      <c r="AH42" s="616" t="n"/>
+      <c r="AI42" s="616" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="359">
       <c r="A43" s="15" t="n"/>
@@ -6027,6 +6205,16 @@
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="15" t="n"/>
       <c r="Y43" s="15" t="n"/>
+      <c r="Z43" s="616" t="n"/>
+      <c r="AA43" s="616" t="n"/>
+      <c r="AB43" s="616" t="n"/>
+      <c r="AC43" s="616" t="n"/>
+      <c r="AD43" s="616" t="n"/>
+      <c r="AE43" s="616" t="n"/>
+      <c r="AF43" s="616" t="n"/>
+      <c r="AG43" s="616" t="n"/>
+      <c r="AH43" s="616" t="n"/>
+      <c r="AI43" s="616" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1" s="359">
       <c r="A44" s="15" t="n"/>
@@ -6054,6 +6242,16 @@
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="15" t="n"/>
       <c r="Y44" s="15" t="n"/>
+      <c r="Z44" s="616" t="n"/>
+      <c r="AA44" s="616" t="n"/>
+      <c r="AB44" s="616" t="n"/>
+      <c r="AC44" s="616" t="n"/>
+      <c r="AD44" s="616" t="n"/>
+      <c r="AE44" s="616" t="n"/>
+      <c r="AF44" s="616" t="n"/>
+      <c r="AG44" s="616" t="n"/>
+      <c r="AH44" s="616" t="n"/>
+      <c r="AI44" s="616" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1" s="359">
       <c r="A45" s="15" t="n"/>
@@ -6081,6 +6279,16 @@
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="15" t="n"/>
       <c r="Y45" s="15" t="n"/>
+      <c r="Z45" s="616" t="n"/>
+      <c r="AA45" s="616" t="n"/>
+      <c r="AB45" s="616" t="n"/>
+      <c r="AC45" s="616" t="n"/>
+      <c r="AD45" s="616" t="n"/>
+      <c r="AE45" s="616" t="n"/>
+      <c r="AF45" s="616" t="n"/>
+      <c r="AG45" s="616" t="n"/>
+      <c r="AH45" s="616" t="n"/>
+      <c r="AI45" s="616" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1" s="359">
       <c r="A46" s="15" t="n"/>
@@ -6108,6 +6316,16 @@
       <c r="W46" s="15" t="n"/>
       <c r="X46" s="15" t="n"/>
       <c r="Y46" s="15" t="n"/>
+      <c r="Z46" s="616" t="n"/>
+      <c r="AA46" s="616" t="n"/>
+      <c r="AB46" s="616" t="n"/>
+      <c r="AC46" s="616" t="n"/>
+      <c r="AD46" s="616" t="n"/>
+      <c r="AE46" s="616" t="n"/>
+      <c r="AF46" s="616" t="n"/>
+      <c r="AG46" s="616" t="n"/>
+      <c r="AH46" s="616" t="n"/>
+      <c r="AI46" s="616" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="359">
       <c r="A47" s="15" t="n"/>
@@ -6135,6 +6353,16 @@
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="15" t="n"/>
       <c r="Y47" s="15" t="n"/>
+      <c r="Z47" s="616" t="n"/>
+      <c r="AA47" s="616" t="n"/>
+      <c r="AB47" s="616" t="n"/>
+      <c r="AC47" s="616" t="n"/>
+      <c r="AD47" s="616" t="n"/>
+      <c r="AE47" s="616" t="n"/>
+      <c r="AF47" s="616" t="n"/>
+      <c r="AG47" s="616" t="n"/>
+      <c r="AH47" s="616" t="n"/>
+      <c r="AI47" s="616" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="359">
       <c r="A48" s="15" t="n"/>
@@ -6162,6 +6390,16 @@
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="15" t="n"/>
       <c r="Y48" s="15" t="n"/>
+      <c r="Z48" s="616" t="n"/>
+      <c r="AA48" s="616" t="n"/>
+      <c r="AB48" s="616" t="n"/>
+      <c r="AC48" s="616" t="n"/>
+      <c r="AD48" s="616" t="n"/>
+      <c r="AE48" s="616" t="n"/>
+      <c r="AF48" s="616" t="n"/>
+      <c r="AG48" s="616" t="n"/>
+      <c r="AH48" s="616" t="n"/>
+      <c r="AI48" s="616" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1" s="359">
       <c r="A49" s="15" t="n"/>
@@ -6189,6 +6427,16 @@
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="15" t="n"/>
       <c r="Y49" s="15" t="n"/>
+      <c r="Z49" s="616" t="n"/>
+      <c r="AA49" s="616" t="n"/>
+      <c r="AB49" s="616" t="n"/>
+      <c r="AC49" s="616" t="n"/>
+      <c r="AD49" s="616" t="n"/>
+      <c r="AE49" s="616" t="n"/>
+      <c r="AF49" s="616" t="n"/>
+      <c r="AG49" s="616" t="n"/>
+      <c r="AH49" s="616" t="n"/>
+      <c r="AI49" s="616" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1" s="359">
       <c r="A50" s="15" t="n"/>
@@ -6216,6 +6464,16 @@
       <c r="W50" s="15" t="n"/>
       <c r="X50" s="15" t="n"/>
       <c r="Y50" s="15" t="n"/>
+      <c r="Z50" s="616" t="n"/>
+      <c r="AA50" s="616" t="n"/>
+      <c r="AB50" s="616" t="n"/>
+      <c r="AC50" s="616" t="n"/>
+      <c r="AD50" s="616" t="n"/>
+      <c r="AE50" s="616" t="n"/>
+      <c r="AF50" s="616" t="n"/>
+      <c r="AG50" s="616" t="n"/>
+      <c r="AH50" s="616" t="n"/>
+      <c r="AI50" s="616" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="359">
       <c r="A51" s="15" t="n"/>
@@ -6243,6 +6501,16 @@
       <c r="W51" s="15" t="n"/>
       <c r="X51" s="15" t="n"/>
       <c r="Y51" s="15" t="n"/>
+      <c r="Z51" s="616" t="n"/>
+      <c r="AA51" s="616" t="n"/>
+      <c r="AB51" s="616" t="n"/>
+      <c r="AC51" s="616" t="n"/>
+      <c r="AD51" s="616" t="n"/>
+      <c r="AE51" s="616" t="n"/>
+      <c r="AF51" s="616" t="n"/>
+      <c r="AG51" s="616" t="n"/>
+      <c r="AH51" s="616" t="n"/>
+      <c r="AI51" s="616" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1" s="359">
       <c r="A52" s="15" t="n"/>
@@ -6270,6 +6538,16 @@
       <c r="W52" s="15" t="n"/>
       <c r="X52" s="15" t="n"/>
       <c r="Y52" s="15" t="n"/>
+      <c r="Z52" s="616" t="n"/>
+      <c r="AA52" s="616" t="n"/>
+      <c r="AB52" s="616" t="n"/>
+      <c r="AC52" s="616" t="n"/>
+      <c r="AD52" s="616" t="n"/>
+      <c r="AE52" s="616" t="n"/>
+      <c r="AF52" s="616" t="n"/>
+      <c r="AG52" s="616" t="n"/>
+      <c r="AH52" s="616" t="n"/>
+      <c r="AI52" s="616" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1" s="359">
       <c r="A53" s="15" t="n"/>
@@ -6297,6 +6575,16 @@
       <c r="W53" s="15" t="n"/>
       <c r="X53" s="15" t="n"/>
       <c r="Y53" s="15" t="n"/>
+      <c r="Z53" s="616" t="n"/>
+      <c r="AA53" s="616" t="n"/>
+      <c r="AB53" s="616" t="n"/>
+      <c r="AC53" s="616" t="n"/>
+      <c r="AD53" s="616" t="n"/>
+      <c r="AE53" s="616" t="n"/>
+      <c r="AF53" s="616" t="n"/>
+      <c r="AG53" s="616" t="n"/>
+      <c r="AH53" s="616" t="n"/>
+      <c r="AI53" s="616" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1" s="359">
       <c r="A54" s="15" t="n"/>
@@ -6324,6 +6612,16 @@
       <c r="W54" s="15" t="n"/>
       <c r="X54" s="15" t="n"/>
       <c r="Y54" s="15" t="n"/>
+      <c r="Z54" s="616" t="n"/>
+      <c r="AA54" s="616" t="n"/>
+      <c r="AB54" s="616" t="n"/>
+      <c r="AC54" s="616" t="n"/>
+      <c r="AD54" s="616" t="n"/>
+      <c r="AE54" s="616" t="n"/>
+      <c r="AF54" s="616" t="n"/>
+      <c r="AG54" s="616" t="n"/>
+      <c r="AH54" s="616" t="n"/>
+      <c r="AI54" s="616" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1" s="359">
       <c r="A55" s="15" t="n"/>
@@ -6351,6 +6649,16 @@
       <c r="W55" s="15" t="n"/>
       <c r="X55" s="15" t="n"/>
       <c r="Y55" s="15" t="n"/>
+      <c r="Z55" s="616" t="n"/>
+      <c r="AA55" s="616" t="n"/>
+      <c r="AB55" s="616" t="n"/>
+      <c r="AC55" s="616" t="n"/>
+      <c r="AD55" s="616" t="n"/>
+      <c r="AE55" s="616" t="n"/>
+      <c r="AF55" s="616" t="n"/>
+      <c r="AG55" s="616" t="n"/>
+      <c r="AH55" s="616" t="n"/>
+      <c r="AI55" s="616" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1" s="359"/>
     <row r="57" ht="18" customHeight="1" s="359"/>
@@ -7298,13 +7606,12 @@
     <row r="999" ht="18" customHeight="1" s="359"/>
     <row r="1000" ht="18" customHeight="1" s="359"/>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="24">
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="L10:M11"/>
     <mergeCell ref="N8:V8"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="Z3:AC4"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="N12:O12"/>
@@ -7323,7 +7630,6 @@
     <mergeCell ref="G19:V19"/>
     <mergeCell ref="A24:X24"/>
     <mergeCell ref="G18:V18"/>
-    <mergeCell ref="Z2:AC2"/>
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:G1 N8:N10 P12 R12 T12">
